--- a/data/shu_tahunan.xlsx
+++ b/data/shu_tahunan.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -433,9 +433,9 @@
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
     <col width="19" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="21" customWidth="1" min="16" max="16"/>
     <col width="50" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
@@ -572,14 +572,88 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Draft</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>super_admin</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2026-05-08 11:23:59</t>
+        </is>
+      </c>
       <c r="Q2" t="inlineStr">
         <is>
           <t>Sumber SHU: Provisi Pinjaman. Tahun: 2026. Pendapatan provisi pinjaman disetujui/lunas: Rp 60,000. Jumlah pinjaman dihitung: 1.
+[AUTO] SHU dihitung otomatis dari pendapatan provisi pinjaman tahun 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>da020475-2831-4e34-9c3b-3e35542188b1</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-05-08 13:12:28</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2060000</v>
+      </c>
+      <c r="E3" t="n">
+        <v>309000</v>
+      </c>
+      <c r="F3" t="n">
+        <v>309000</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1030000</v>
+      </c>
+      <c r="H3" t="n">
+        <v>103000</v>
+      </c>
+      <c r="I3" t="n">
+        <v>10300</v>
+      </c>
+      <c r="J3" t="n">
+        <v>41200</v>
+      </c>
+      <c r="K3" t="n">
+        <v>10300</v>
+      </c>
+      <c r="L3" t="n">
+        <v>206000</v>
+      </c>
+      <c r="M3" t="n">
+        <v>41200</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>super_admin</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2026-05-08 13:12:51</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Sumber SHU: Provisi Pinjaman. Tahun: 2026. Pendapatan provisi pinjaman disetujui/lunas: Rp 2,060,000. Jumlah pinjaman dihitung: 1.
 [AUTO] SHU dihitung otomatis dari pendapatan provisi pinjaman tahun 2026.</t>
         </is>
       </c>
